--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU02/HRM/pre LAM_HRM-2031-0380/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.88477</v>
+        <v>16.82146</v>
       </c>
       <c r="D2" t="n">
-        <v>16.34192</v>
+        <v>16.33285</v>
       </c>
       <c r="E2" t="n">
-        <v>16.72912</v>
+        <v>16.8105</v>
       </c>
       <c r="F2" t="n">
-        <v>42.30247</v>
+        <v>42.08817</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05086</v>
+        <v>0.05078</v>
       </c>
       <c r="H2" t="n">
-        <v>1.85211</v>
+        <v>1.81427</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.97814</v>
+        <v>16.70071</v>
       </c>
       <c r="D3" t="n">
-        <v>16.69559</v>
+        <v>16.43449</v>
       </c>
       <c r="E3" t="n">
-        <v>16.70924</v>
+        <v>16.6723</v>
       </c>
       <c r="F3" t="n">
-        <v>42.16786</v>
+        <v>41.85484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04998</v>
+        <v>0.04973</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84152</v>
+        <v>1.81182</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.02249</v>
+        <v>16.54045</v>
       </c>
       <c r="D4" t="n">
-        <v>16.63938</v>
+        <v>16.23649</v>
       </c>
       <c r="E4" t="n">
-        <v>16.62089</v>
+        <v>16.30323</v>
       </c>
       <c r="F4" t="n">
-        <v>42.3824</v>
+        <v>42.5252</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05049</v>
+        <v>0.05048</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81177</v>
+        <v>1.83833</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.57159</v>
+        <v>16.51272</v>
       </c>
       <c r="D6" t="n">
-        <v>15.79364</v>
+        <v>16.05879</v>
       </c>
       <c r="E6" t="n">
-        <v>16.2826</v>
+        <v>16.22357</v>
       </c>
       <c r="F6" t="n">
-        <v>21.55431</v>
+        <v>21.65977</v>
       </c>
       <c r="G6" t="n">
-        <v>33.78895</v>
+        <v>34.35029</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.46145</v>
+        <v>16.9243</v>
       </c>
       <c r="D7" t="n">
-        <v>16.17124</v>
+        <v>16.18999</v>
       </c>
       <c r="E7" t="n">
-        <v>16.65967</v>
+        <v>16.29941</v>
       </c>
       <c r="F7" t="n">
-        <v>21.21105</v>
+        <v>21.62815</v>
       </c>
       <c r="G7" t="n">
-        <v>33.55049</v>
+        <v>34.37534</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.60326</v>
+        <v>16.86011</v>
       </c>
       <c r="D8" t="n">
-        <v>15.88238</v>
+        <v>15.88825</v>
       </c>
       <c r="E8" t="n">
-        <v>16.37088</v>
+        <v>16.52592</v>
       </c>
       <c r="F8" t="n">
-        <v>21.35065</v>
+        <v>21.56136</v>
       </c>
       <c r="G8" t="n">
-        <v>34.21022</v>
+        <v>34.63722</v>
       </c>
     </row>
   </sheetData>
